--- a/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
@@ -617,10 +617,10 @@
         <v>0.35</v>
       </c>
       <c r="G13" t="n">
-        <v>2.9</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="14">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>17.61</v>
+        <v>20.8</v>
       </c>
     </row>
     <row r="15">
@@ -730,10 +730,10 @@
         <v>1</v>
       </c>
       <c r="G20" t="n">
-        <v>27.76</v>
+        <v>30.95</v>
       </c>
       <c r="H20" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
     </row>
     <row r="21">
@@ -749,7 +749,7 @@
       </c>
       <c r="G21" s="4" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>28.04</v>
+        <v>31.26</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 12 Instalaciones sanitarias</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Aparatos sanitarios y grifería</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-12-04-020.xlsx
@@ -485,7 +485,7 @@
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Instalación de lavamanos, ya sea de pedestal, sobre encimera o suspendido, sobre puntos de agua y desagüe previamente ejecutados. Incluye replanteo de la altura de uso, taladrado y anclaje al paramento o fijación sobre el mueble, montaje de la grifería con sus juntas, conexión de las tomas de agua fría y caliente mediante tubos de abasto flexibles con llaves de escuadra, montaje del desagüe con su válvula y sifón, sellado perimetral con silicona sanitaria, y prueba de funcionamiento, evacuación y estanqueidad. El aparato y la grifería los elige el cliente y se presupuestan aparte. Medido por unidad instalada y probada.
+          <t xml:space="preserve">Instalación de lavamanos, ya sea de pedestal, sobre mesón o suspendido, sobre puntos de agua y desagüe previamente ejecutados. Incluye replanteo de la altura de uso, taladrado y anclaje al paramento o fijación sobre el mueble, montaje de la grifería con sus juntas, conexión de las tomas de agua fría y caliente mediante tubos de abasto flexibles con llaves de escuadra, montaje del desagüe con su válvula y sifón, sellado perimetral con silicona sanitaria, y prueba de funcionamiento, evacuación y estanqueidad. El aparato y la grifería los elige el cliente y se presupuestan aparte. Medido por unidad instalada y probada.
 </t>
         </is>
       </c>
